--- a/data/trans_dic/Hacinamiento_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 10,0</t>
+          <t>5,22; 9,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,72</t>
+          <t>3,26; 7,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,75</t>
+          <t>5,14; 10,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 8,7</t>
+          <t>1,17; 9,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 11,11</t>
+          <t>6,07; 11,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 12,48</t>
+          <t>6,7; 12,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,69</t>
+          <t>4,61; 9,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 12,79</t>
+          <t>3,87; 12,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,63</t>
+          <t>6,23; 9,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,0</t>
+          <t>5,49; 9,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,27</t>
+          <t>5,64; 9,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 8,84</t>
+          <t>2,72; 8,83</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,34</t>
+          <t>4,55; 8,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,56</t>
+          <t>3,08; 6,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,85</t>
+          <t>4,52; 8,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,2</t>
+          <t>0,08; 3,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,16</t>
+          <t>5,99; 10,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 12,11</t>
+          <t>7,53; 12,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,36</t>
+          <t>3,82; 7,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,35</t>
+          <t>0,72; 3,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 8,5</t>
+          <t>5,61; 8,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 8,64</t>
+          <t>5,77; 8,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,47</t>
+          <t>4,59; 7,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,48</t>
+          <t>0,72; 2,47</t>
         </is>
       </c>
     </row>
@@ -997,47 +997,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,17</t>
+          <t>2,69; 6,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,8</t>
+          <t>5,81; 9,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,57</t>
+          <t>2,96; 6,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,23</t>
+          <t>2,59; 6,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,83</t>
+          <t>6,04; 10,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 13,14</t>
+          <t>8,3; 13,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,11</t>
+          <t>5,22; 9,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,69</t>
+          <t>3,53; 6,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,73</t>
+          <t>4,91; 7,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,14</t>
+          <t>4,61; 7,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,95</t>
+          <t>3,39; 5,94</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,77</t>
+          <t>2,35; 5,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,34</t>
+          <t>2,96; 6,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,7</t>
+          <t>2,35; 6,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,56</t>
+          <t>0,79; 3,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 7,44</t>
+          <t>3,34; 7,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,15</t>
+          <t>2,43; 5,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,73</t>
+          <t>2,79; 5,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,7</t>
+          <t>1,71; 3,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,86</t>
+          <t>3,27; 6,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,56</t>
+          <t>3,1; 5,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,19</t>
+          <t>2,85; 5,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,1</t>
+          <t>1,32; 3,23</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,52</t>
+          <t>2,38; 6,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,16</t>
+          <t>1,52; 5,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,17</t>
+          <t>1,1; 4,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,57</t>
+          <t>1,08; 3,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,43</t>
+          <t>2,56; 6,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,91</t>
+          <t>1,63; 4,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,16</t>
+          <t>1,67; 5,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,1</t>
+          <t>0,67; 2,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,57</t>
+          <t>2,76; 5,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,23</t>
+          <t>2,0; 4,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,96</t>
+          <t>1,66; 4,14</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,49</t>
+          <t>1,06; 2,53</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,66</t>
+          <t>1,63; 5,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,72</t>
+          <t>1,74; 6,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,77</t>
+          <t>0,9; 4,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,54</t>
+          <t>1,02; 3,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,62</t>
+          <t>0,82; 3,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,64</t>
+          <t>0,27; 2,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,57</t>
+          <t>1,13; 4,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,2</t>
+          <t>0,1; 1,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,89</t>
+          <t>1,49; 3,95</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,45</t>
+          <t>1,11; 3,39</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,55</t>
+          <t>1,27; 3,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,82</t>
+          <t>0,49; 1,72</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,83</t>
+          <t>0,78; 4,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,66</t>
+          <t>0,84; 4,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,19</t>
+          <t>0,34; 3,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,53</t>
+          <t>0,3; 2,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,14</t>
+          <t>1,01; 4,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,2</t>
+          <t>0,56; 3,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,44</t>
+          <t>0,53; 4,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,21</t>
+          <t>0,04; 1,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,56</t>
+          <t>1,05; 3,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,05</t>
+          <t>0,87; 2,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,06</t>
+          <t>0,65; 3,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,31</t>
+          <t>0,24; 1,25</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,6</t>
+          <t>4,1; 5,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,11; 5,66</t>
+          <t>4,04; 5,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,08</t>
+          <t>3,6; 4,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,07</t>
+          <t>1,63; 2,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,17; 6,9</t>
+          <t>5,14; 6,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,05</t>
+          <t>5,38; 7,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,87; 5,34</t>
+          <t>3,92; 5,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,13</t>
+          <t>1,89; 3,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,03</t>
+          <t>4,87; 6,02</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,06</t>
+          <t>5,01; 6,05</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,92; 4,93</t>
+          <t>3,93; 4,93</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,94; 2,84</t>
+          <t>1,93; 2,84</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25954; 49237</t>
+          <t>25709; 49125</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14504; 34948</t>
+          <t>14752; 34088</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22844; 44987</t>
+          <t>21506; 45152</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4162; 34167</t>
+          <t>4591; 37902</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28516; 51811</t>
+          <t>28336; 53159</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29048; 53690</t>
+          <t>28824; 53451</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18126; 37981</t>
+          <t>18081; 38481</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12687; 40072</t>
+          <t>12111; 39595</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59266; 92320</t>
+          <t>59729; 93959</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48302; 79505</t>
+          <t>48521; 80004</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44254; 75122</t>
+          <t>45660; 78070</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21003; 62418</t>
+          <t>19223; 62336</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32302; 61051</t>
+          <t>33302; 61416</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22071; 45081</t>
+          <t>21142; 45036</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26969; 51904</t>
+          <t>26506; 52079</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>505; 13498</t>
+          <t>330; 16025</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36154; 63355</t>
+          <t>37346; 65047</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45644; 73797</t>
+          <t>45903; 75669</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20429; 41030</t>
+          <t>21282; 41640</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4040; 16958</t>
+          <t>3644; 16763</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>76300; 115214</t>
+          <t>76105; 117672</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74435; 112034</t>
+          <t>74794; 111815</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52126; 85472</t>
+          <t>52500; 83590</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6844; 23004</t>
+          <t>6653; 22906</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16558; 39299</t>
+          <t>17107; 39397</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40055; 66798</t>
+          <t>39648; 67788</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20955; 43841</t>
+          <t>19749; 42790</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13840; 33226</t>
+          <t>13788; 33924</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43730; 74731</t>
+          <t>41641; 73269</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58077; 93303</t>
+          <t>58909; 92530</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34581; 60243</t>
+          <t>34507; 60145</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20032; 39506</t>
+          <t>20879; 40456</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>66155; 102519</t>
+          <t>65143; 100903</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>105711; 149036</t>
+          <t>105726; 149029</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61655; 94905</t>
+          <t>61255; 96309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38282; 66878</t>
+          <t>38137; 66770</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12396; 29841</t>
+          <t>12175; 29873</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17430; 38535</t>
+          <t>17996; 39408</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14907; 36596</t>
+          <t>15079; 39553</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7187; 31540</t>
+          <t>7006; 30945</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16882; 38054</t>
+          <t>17081; 36942</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15835; 37513</t>
+          <t>14812; 36360</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17106; 37026</t>
+          <t>18024; 38135</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12364; 26086</t>
+          <t>12023; 26444</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32578; 60281</t>
+          <t>33660; 62084</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37316; 67634</t>
+          <t>37734; 67648</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37001; 66886</t>
+          <t>36642; 67576</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21867; 49365</t>
+          <t>21045; 51375</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9143; 25207</t>
+          <t>9197; 24106</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7197; 22165</t>
+          <t>6546; 22163</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4577; 19754</t>
+          <t>5189; 21842</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5604; 19812</t>
+          <t>6000; 21427</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9687; 25967</t>
+          <t>10327; 26731</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7665; 21858</t>
+          <t>7279; 21846</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9232; 25577</t>
+          <t>8273; 25914</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3493; 11322</t>
+          <t>3591; 11194</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22541; 44038</t>
+          <t>21790; 44756</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17502; 37032</t>
+          <t>17482; 37735</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17854; 38420</t>
+          <t>16098; 40151</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10752; 27272</t>
+          <t>11647; 27702</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4855; 16508</t>
+          <t>4760; 17344</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5227; 17651</t>
+          <t>5364; 18529</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2091; 12523</t>
+          <t>2985; 13284</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3812; 12942</t>
+          <t>3737; 12659</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2713; 12351</t>
+          <t>2787; 13164</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>940; 9329</t>
+          <t>944; 8810</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3781; 17211</t>
+          <t>4270; 17772</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>583; 7212</t>
+          <t>576; 7591</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9806; 24583</t>
+          <t>9403; 24983</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7293; 22811</t>
+          <t>7322; 22454</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9047; 25166</t>
+          <t>8987; 25220</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4692; 17628</t>
+          <t>4710; 16647</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1663; 10147</t>
+          <t>1636; 9907</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1109; 11487</t>
+          <t>2069; 11772</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1481; 10675</t>
+          <t>872; 10045</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>832; 7036</t>
+          <t>839; 6656</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2332; 13831</t>
+          <t>3374; 14736</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2156; 12361</t>
+          <t>2165; 12793</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1345; 13641</t>
+          <t>2088; 16400</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>159; 5086</t>
+          <t>160; 5295</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6051; 19383</t>
+          <t>5703; 19952</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5427; 19282</t>
+          <t>5529; 18865</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4341; 19943</t>
+          <t>4261; 19512</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1478; 9183</t>
+          <t>1647; 8740</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>132020; 183004</t>
+          <t>133944; 187136</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>140369; 193221</t>
+          <t>137796; 188694</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>122364; 171312</t>
+          <t>121449; 167990</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56636; 105425</t>
+          <t>56103; 100191</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>174184; 232663</t>
+          <t>173320; 231291</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>192329; 250007</t>
+          <t>190703; 249600</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>136608; 188378</t>
+          <t>138065; 189847</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>70590; 114945</t>
+          <t>69417; 114009</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>322844; 400050</t>
+          <t>323144; 399602</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>342485; 421320</t>
+          <t>348380; 421226</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>270698; 340004</t>
+          <t>270888; 339895</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>137769; 201908</t>
+          <t>136957; 201799</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,27 +684,27 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>7,28%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,98</t>
+          <t>5,06; 9,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,53</t>
+          <t>3,22; 7,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 10,79</t>
+          <t>5,28; 10,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 9,65</t>
+          <t>1,19; 7,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 11,39</t>
+          <t>6,18; 11,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 12,42</t>
+          <t>6,79; 12,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 9,82</t>
+          <t>4,59; 9,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 12,64</t>
+          <t>4,15; 12,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,8</t>
+          <t>6,27; 9,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 9,06</t>
+          <t>5,51; 8,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,64</t>
+          <t>5,58; 9,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,83</t>
+          <t>3,25; 8,28</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,39</t>
+          <t>4,52; 8,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,55</t>
+          <t>3,3; 6,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,52; 8,88</t>
+          <t>4,43; 8,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,79</t>
+          <t>0,5; 3,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 10,43</t>
+          <t>5,77; 10,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 12,42</t>
+          <t>7,47; 12,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,47</t>
+          <t>3,8; 7,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,31</t>
+          <t>1,53; 4,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,68</t>
+          <t>5,48; 8,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 8,63</t>
+          <t>5,79; 8,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,31</t>
+          <t>4,62; 7,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,47</t>
+          <t>1,22; 3,21</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,19</t>
+          <t>2,57; 6,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 9,94</t>
+          <t>5,85; 10,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,41</t>
+          <t>3,12; 6,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,36</t>
+          <t>3,4; 7,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 10,62</t>
+          <t>6,32; 10,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,3; 13,04</t>
+          <t>8,08; 12,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,09</t>
+          <t>5,15; 9,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,85</t>
+          <t>5,37; 8,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 7,61</t>
+          <t>5,01; 7,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,6; 10,71</t>
+          <t>7,7; 10,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,25</t>
+          <t>4,58; 7,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,94</t>
+          <t>4,8; 7,33</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,78</t>
+          <t>2,5; 6,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,49</t>
+          <t>3,04; 6,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,16</t>
+          <t>2,37; 5,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,5</t>
+          <t>2,02; 4,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 7,22</t>
+          <t>3,14; 7,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,96</t>
+          <t>2,59; 5,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,9</t>
+          <t>2,67; 5,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,75</t>
+          <t>2,3; 4,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,04</t>
+          <t>3,32; 5,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,56</t>
+          <t>3,1; 5,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,25</t>
+          <t>2,97; 5,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,23</t>
+          <t>2,43; 4,15</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,23</t>
+          <t>2,48; 6,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,16</t>
+          <t>1,54; 5,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,61</t>
+          <t>1,1; 4,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,86</t>
+          <t>1,2; 3,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,62</t>
+          <t>2,45; 6,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,9</t>
+          <t>1,61; 5,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,23</t>
+          <t>1,67; 5,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,08</t>
+          <t>0,68; 2,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,66</t>
+          <t>2,73; 5,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,31</t>
+          <t>1,9; 4,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,14</t>
+          <t>1,83; 4,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,53</t>
+          <t>1,1; 2,48</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,94</t>
+          <t>1,71; 5,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,0</t>
+          <t>1,68; 6,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,0</t>
+          <t>0,63; 3,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,46</t>
+          <t>0,99; 3,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,86</t>
+          <t>0,82; 3,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,5</t>
+          <t>0,27; 2,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,72</t>
+          <t>1,1; 4,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,26</t>
+          <t>0,31; 2,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,95</t>
+          <t>1,51; 4,08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,39</t>
+          <t>1,14; 3,38</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,56</t>
+          <t>1,2; 3,6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,72</t>
+          <t>0,77; 2,19</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,72</t>
+          <t>0,8; 4,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,77</t>
+          <t>0,84; 5,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,95</t>
+          <t>0,34; 4,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,39</t>
+          <t>0,26; 2,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,41</t>
+          <t>0,7; 4,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,32</t>
+          <t>0,57; 3,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,13</t>
+          <t>0,34; 3,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,26</t>
+          <t>0,14; 1,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,67</t>
+          <t>1,05; 3,62</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,98</t>
+          <t>0,85; 3,17</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,0</t>
+          <t>0,67; 3,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,25</t>
+          <t>0,28; 1,38</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,1; 5,73</t>
+          <t>4,08; 5,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,53</t>
+          <t>4,1; 5,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,6; 4,98</t>
+          <t>3,6; 5,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,92</t>
+          <t>2,18; 3,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,86</t>
+          <t>5,18; 6,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,38; 7,04</t>
+          <t>5,45; 7,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,92; 5,38</t>
+          <t>3,85; 5,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,1</t>
+          <t>2,75; 3,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,87; 6,02</t>
+          <t>4,81; 5,94</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,05</t>
+          <t>4,95; 6,06</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,93; 4,93</t>
+          <t>3,91; 4,93</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,84</t>
+          <t>2,63; 3,45</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>26931</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35711</t>
+          <t>39226</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25709; 49125</t>
+          <t>24917; 48677</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14752; 34088</t>
+          <t>14588; 34980</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21506; 45152</t>
+          <t>22090; 45732</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4591; 37902</t>
+          <t>4764; 29736</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28336; 53159</t>
+          <t>28840; 52130</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28824; 53451</t>
+          <t>29209; 53267</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18081; 38481</t>
+          <t>17981; 38854</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12111; 39595</t>
+          <t>15035; 44501</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59729; 93959</t>
+          <t>60127; 93084</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48521; 80004</t>
+          <t>48660; 78900</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45660; 78070</t>
+          <t>45220; 76729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19223; 62336</t>
+          <t>24785; 63176</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12649</t>
+          <t>20019</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33302; 61416</t>
+          <t>33107; 62003</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21142; 45036</t>
+          <t>22670; 46592</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26506; 52079</t>
+          <t>25954; 49040</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>330; 16025</t>
+          <t>2389; 16984</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37346; 65047</t>
+          <t>35972; 65142</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45903; 75669</t>
+          <t>45533; 75152</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21282; 41640</t>
+          <t>21193; 42112</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3644; 16763</t>
+          <t>7601; 23208</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>76105; 117672</t>
+          <t>74218; 116443</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74794; 111815</t>
+          <t>75043; 111662</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52500; 83590</t>
+          <t>52857; 85307</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6653; 22906</t>
+          <t>11879; 31226</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22110</t>
+          <t>31343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29557</t>
+          <t>43447</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51667</t>
+          <t>74790</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17107; 39397</t>
+          <t>16353; 39133</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39648; 67788</t>
+          <t>39885; 68943</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19749; 42790</t>
+          <t>20849; 42347</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13788; 33924</t>
+          <t>20940; 44363</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>41641; 73269</t>
+          <t>43614; 73192</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58909; 92530</t>
+          <t>57341; 91766</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34507; 60145</t>
+          <t>34080; 59744</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20879; 40456</t>
+          <t>33342; 55351</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65143; 100903</t>
+          <t>66396; 103159</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>105726; 149029</t>
+          <t>107179; 148348</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61255; 96309</t>
+          <t>60895; 94277</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38137; 66770</t>
+          <t>59377; 90771</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18552</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36505</t>
+          <t>45291</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12175; 29873</t>
+          <t>12902; 32369</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17996; 39408</t>
+          <t>18442; 39319</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15079; 39553</t>
+          <t>15240; 37976</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7006; 30945</t>
+          <t>14117; 34054</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17081; 36942</t>
+          <t>16064; 36768</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14812; 36360</t>
+          <t>15809; 36353</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18024; 38135</t>
+          <t>17232; 36881</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12023; 26444</t>
+          <t>16727; 32170</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33660; 62084</t>
+          <t>34174; 59841</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37734; 67648</t>
+          <t>37695; 67777</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36642; 67576</t>
+          <t>38192; 68131</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21045; 51375</t>
+          <t>34615; 59111</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17767</t>
+          <t>20636</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9197; 24106</t>
+          <t>9582; 24553</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6546; 22163</t>
+          <t>6596; 21515</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5189; 21842</t>
+          <t>5212; 19696</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6000; 21427</t>
+          <t>7251; 22017</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10327; 26731</t>
+          <t>9888; 26734</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7279; 21846</t>
+          <t>7186; 22465</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8273; 25914</t>
+          <t>8299; 25708</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3591; 11194</t>
+          <t>4112; 12730</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21790; 44756</t>
+          <t>21592; 43532</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17482; 37735</t>
+          <t>16629; 37145</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16098; 40151</t>
+          <t>17770; 39804</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11647; 27702</t>
+          <t>13262; 29818</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>11618</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4760; 17344</t>
+          <t>4976; 17286</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5364; 18529</t>
+          <t>5184; 19281</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2985; 13284</t>
+          <t>2082; 13022</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3737; 12659</t>
+          <t>4018; 14066</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2787; 13164</t>
+          <t>2801; 13212</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>944; 8810</t>
+          <t>942; 8041</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4270; 17772</t>
+          <t>4145; 17199</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>576; 7591</t>
+          <t>1348; 8682</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9403; 24983</t>
+          <t>9580; 25785</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7322; 22454</t>
+          <t>7555; 22362</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8987; 25220</t>
+          <t>8521; 25520</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4710; 16647</t>
+          <t>6424; 18368</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>5396</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1636; 9907</t>
+          <t>1670; 9327</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2069; 11772</t>
+          <t>2073; 12579</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>872; 10045</t>
+          <t>868; 10437</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>839; 6656</t>
+          <t>806; 8380</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3374; 14736</t>
+          <t>2341; 14609</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2165; 12793</t>
+          <t>2185; 14315</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2088; 16400</t>
+          <t>1343; 14781</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>160; 5295</t>
+          <t>642; 6540</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5703; 19952</t>
+          <t>5694; 19671</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5529; 18865</t>
+          <t>5387; 20078</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4261; 19512</t>
+          <t>4346; 20018</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1647; 8740</t>
+          <t>2139; 10551</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77848</t>
+          <t>96365</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>90986</t>
+          <t>120611</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>168834</t>
+          <t>216975</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>133944; 187136</t>
+          <t>133114; 185742</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>137796; 188694</t>
+          <t>139961; 188220</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>121449; 167990</t>
+          <t>121365; 171510</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56103; 100191</t>
+          <t>76391; 118263</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>173320; 231291</t>
+          <t>174603; 230064</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>190703; 249600</t>
+          <t>193119; 250564</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>138065; 189847</t>
+          <t>135844; 185701</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>69417; 114009</t>
+          <t>101730; 144358</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>323144; 399602</t>
+          <t>319328; 394110</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>348380; 421226</t>
+          <t>344656; 421901</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>270888; 339895</t>
+          <t>270054; 339993</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>136957; 201799</t>
+          <t>189584; 248382</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
